--- a/04_Network/01_Build_Modules/c_data/01_build_modules.xlsx
+++ b/04_Network/01_Build_Modules/c_data/01_build_modules.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6033" uniqueCount="4047">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6069" uniqueCount="4070">
   <si>
     <t>sheet</t>
   </si>
@@ -11722,6 +11722,15 @@
     <t>0.1-6</t>
   </si>
   <si>
+    <t>BiocGenerics</t>
+  </si>
+  <si>
+    <t>0.58.0</t>
+  </si>
+  <si>
+    <t>Bioconductor 3.23 (R 4.6.0)</t>
+  </si>
+  <si>
     <t>BiocManager</t>
   </si>
   <si>
@@ -11740,12 +11749,24 @@
     <t>2.3.4</t>
   </si>
   <si>
+    <t>circlize</t>
+  </si>
+  <si>
+    <t>0.4.18</t>
+  </si>
+  <si>
     <t>cli</t>
   </si>
   <si>
     <t>3.6.6</t>
   </si>
   <si>
+    <t>clue</t>
+  </si>
+  <si>
+    <t>0.3-68</t>
+  </si>
+  <si>
     <t>cluster</t>
   </si>
   <si>
@@ -11764,6 +11785,18 @@
     <t>2.1-2</t>
   </si>
   <si>
+    <t>ComplexHeatmap</t>
+  </si>
+  <si>
+    <t>2.28.0</t>
+  </si>
+  <si>
+    <t>crayon</t>
+  </si>
+  <si>
+    <t>1.5.3</t>
+  </si>
+  <si>
     <t>data.table</t>
   </si>
   <si>
@@ -11842,12 +11875,21 @@
     <t>0.1.4</t>
   </si>
   <si>
+    <t>GetoptLong</t>
+  </si>
+  <si>
+    <t>1.1.1</t>
+  </si>
+  <si>
     <t>ggplot2</t>
   </si>
   <si>
     <t>4.0.3</t>
   </si>
   <si>
+    <t>GlobalOptions</t>
+  </si>
+  <si>
     <t>glue</t>
   </si>
   <si>
@@ -11902,7 +11944,10 @@
     <t>1.86.0</t>
   </si>
   <si>
-    <t>Bioconductor 3.23 (R 4.6.0)</t>
+    <t>IRanges</t>
+  </si>
+  <si>
+    <t>2.46.0</t>
   </si>
   <si>
     <t>iterators</t>
@@ -12004,6 +12049,12 @@
     <t>2.0.3</t>
   </si>
   <si>
+    <t>png</t>
+  </si>
+  <si>
+    <t>0.1-9</t>
+  </si>
+  <si>
     <t>preprocessCore</t>
   </si>
   <si>
@@ -12058,6 +12109,12 @@
     <t>1.2.3</t>
   </si>
   <si>
+    <t>rjson</t>
+  </si>
+  <si>
+    <t>0.2.23</t>
+  </si>
+  <si>
     <t>rlang</t>
   </si>
   <si>
@@ -12088,6 +12145,12 @@
     <t>0.18.0</t>
   </si>
   <si>
+    <t>S4Vectors</t>
+  </si>
+  <si>
+    <t>0.50.0</t>
+  </si>
+  <si>
     <t>S7</t>
   </si>
   <si>
@@ -12104,6 +12167,12 @@
   </si>
   <si>
     <t>1.2.4</t>
+  </si>
+  <si>
+    <t>shape</t>
+  </si>
+  <si>
+    <t>1.4.6.1</t>
   </si>
   <si>
     <t>stringi</t>
@@ -40515,7 +40584,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C77"/>
+  <dimension ref="A1:C89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -40559,15 +40628,15 @@
         <v>3901</v>
       </c>
       <c r="C4" t="s">
-        <v>3897</v>
+        <v>3902</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>3902</v>
+        <v>3903</v>
       </c>
       <c r="B5" t="s">
-        <v>3903</v>
+        <v>3904</v>
       </c>
       <c r="C5" t="s">
         <v>3897</v>
@@ -40575,10 +40644,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>3904</v>
+        <v>3905</v>
       </c>
       <c r="B6" t="s">
-        <v>3905</v>
+        <v>3906</v>
       </c>
       <c r="C6" t="s">
         <v>3897</v>
@@ -40586,10 +40655,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>3906</v>
+        <v>3907</v>
       </c>
       <c r="B7" t="s">
-        <v>3907</v>
+        <v>3908</v>
       </c>
       <c r="C7" t="s">
         <v>3897</v>
@@ -40597,10 +40666,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>3908</v>
+        <v>3909</v>
       </c>
       <c r="B8" t="s">
-        <v>3909</v>
+        <v>3910</v>
       </c>
       <c r="C8" t="s">
         <v>3897</v>
@@ -40608,10 +40677,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>3910</v>
+        <v>3911</v>
       </c>
       <c r="B9" t="s">
-        <v>3911</v>
+        <v>3912</v>
       </c>
       <c r="C9" t="s">
         <v>3897</v>
@@ -40619,10 +40688,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>3912</v>
+        <v>3913</v>
       </c>
       <c r="B10" t="s">
-        <v>3913</v>
+        <v>3914</v>
       </c>
       <c r="C10" t="s">
         <v>3897</v>
@@ -40630,10 +40699,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>3914</v>
+        <v>3915</v>
       </c>
       <c r="B11" t="s">
-        <v>3915</v>
+        <v>3916</v>
       </c>
       <c r="C11" t="s">
         <v>3897</v>
@@ -40641,10 +40710,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>3916</v>
+        <v>3917</v>
       </c>
       <c r="B12" t="s">
-        <v>3917</v>
+        <v>3918</v>
       </c>
       <c r="C12" t="s">
         <v>3897</v>
@@ -40652,10 +40721,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>3918</v>
+        <v>3919</v>
       </c>
       <c r="B13" t="s">
-        <v>3919</v>
+        <v>3920</v>
       </c>
       <c r="C13" t="s">
         <v>3897</v>
@@ -40663,21 +40732,21 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>3920</v>
+        <v>3921</v>
       </c>
       <c r="B14" t="s">
-        <v>3921</v>
+        <v>3922</v>
       </c>
       <c r="C14" t="s">
-        <v>3897</v>
+        <v>3902</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>3922</v>
+        <v>3923</v>
       </c>
       <c r="B15" t="s">
-        <v>3923</v>
+        <v>3924</v>
       </c>
       <c r="C15" t="s">
         <v>3897</v>
@@ -40685,10 +40754,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>3924</v>
+        <v>3925</v>
       </c>
       <c r="B16" t="s">
-        <v>3925</v>
+        <v>3926</v>
       </c>
       <c r="C16" t="s">
         <v>3897</v>
@@ -40696,10 +40765,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>3926</v>
+        <v>3927</v>
       </c>
       <c r="B17" t="s">
-        <v>3927</v>
+        <v>3928</v>
       </c>
       <c r="C17" t="s">
         <v>3897</v>
@@ -40707,10 +40776,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>3928</v>
+        <v>3929</v>
       </c>
       <c r="B18" t="s">
-        <v>3929</v>
+        <v>3930</v>
       </c>
       <c r="C18" t="s">
         <v>3897</v>
@@ -40718,10 +40787,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>3930</v>
+        <v>3931</v>
       </c>
       <c r="B19" t="s">
-        <v>3931</v>
+        <v>3932</v>
       </c>
       <c r="C19" t="s">
         <v>3897</v>
@@ -40729,10 +40798,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>3932</v>
+        <v>3933</v>
       </c>
       <c r="B20" t="s">
-        <v>3933</v>
+        <v>3934</v>
       </c>
       <c r="C20" t="s">
         <v>3897</v>
@@ -40740,10 +40809,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>3934</v>
+        <v>3935</v>
       </c>
       <c r="B21" t="s">
-        <v>3935</v>
+        <v>3936</v>
       </c>
       <c r="C21" t="s">
         <v>3897</v>
@@ -40751,10 +40820,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>3936</v>
+        <v>3937</v>
       </c>
       <c r="B22" t="s">
-        <v>3937</v>
+        <v>3938</v>
       </c>
       <c r="C22" t="s">
         <v>3897</v>
@@ -40762,10 +40831,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>3938</v>
+        <v>3939</v>
       </c>
       <c r="B23" t="s">
-        <v>3939</v>
+        <v>3940</v>
       </c>
       <c r="C23" t="s">
         <v>3897</v>
@@ -40773,10 +40842,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>3940</v>
+        <v>3941</v>
       </c>
       <c r="B24" t="s">
-        <v>3941</v>
+        <v>3942</v>
       </c>
       <c r="C24" t="s">
         <v>3897</v>
@@ -40784,10 +40853,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>3942</v>
+        <v>3943</v>
       </c>
       <c r="B25" t="s">
-        <v>3943</v>
+        <v>3944</v>
       </c>
       <c r="C25" t="s">
         <v>3897</v>
@@ -40795,10 +40864,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>3944</v>
+        <v>3945</v>
       </c>
       <c r="B26" t="s">
-        <v>3945</v>
+        <v>3946</v>
       </c>
       <c r="C26" t="s">
         <v>3897</v>
@@ -40806,10 +40875,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>3946</v>
+        <v>3947</v>
       </c>
       <c r="B27" t="s">
-        <v>3947</v>
+        <v>3948</v>
       </c>
       <c r="C27" t="s">
         <v>3897</v>
@@ -40817,10 +40886,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>3948</v>
+        <v>3949</v>
       </c>
       <c r="B28" t="s">
-        <v>3949</v>
+        <v>3950</v>
       </c>
       <c r="C28" t="s">
         <v>3897</v>
@@ -40828,10 +40897,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>3950</v>
+        <v>3951</v>
       </c>
       <c r="B29" t="s">
-        <v>3951</v>
+        <v>3952</v>
       </c>
       <c r="C29" t="s">
         <v>3897</v>
@@ -40839,10 +40908,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>3952</v>
+        <v>3953</v>
       </c>
       <c r="B30" t="s">
-        <v>3953</v>
+        <v>3954</v>
       </c>
       <c r="C30" t="s">
         <v>3897</v>
@@ -40850,10 +40919,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>3954</v>
+        <v>3955</v>
       </c>
       <c r="B31" t="s">
-        <v>3955</v>
+        <v>3950</v>
       </c>
       <c r="C31" t="s">
         <v>3897</v>
@@ -40878,15 +40947,15 @@
         <v>3959</v>
       </c>
       <c r="C33" t="s">
-        <v>3960</v>
+        <v>3897</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
+        <v>3960</v>
+      </c>
+      <c r="B34" t="s">
         <v>3961</v>
-      </c>
-      <c r="B34" t="s">
-        <v>3962</v>
       </c>
       <c r="C34" t="s">
         <v>3897</v>
@@ -40894,10 +40963,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
+        <v>3962</v>
+      </c>
+      <c r="B35" t="s">
         <v>3963</v>
-      </c>
-      <c r="B35" t="s">
-        <v>3964</v>
       </c>
       <c r="C35" t="s">
         <v>3897</v>
@@ -40905,10 +40974,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
+        <v>3964</v>
+      </c>
+      <c r="B36" t="s">
         <v>3965</v>
-      </c>
-      <c r="B36" t="s">
-        <v>3966</v>
       </c>
       <c r="C36" t="s">
         <v>3897</v>
@@ -40916,10 +40985,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
+        <v>3966</v>
+      </c>
+      <c r="B37" t="s">
         <v>3967</v>
-      </c>
-      <c r="B37" t="s">
-        <v>3968</v>
       </c>
       <c r="C37" t="s">
         <v>3897</v>
@@ -40927,10 +40996,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
+        <v>3968</v>
+      </c>
+      <c r="B38" t="s">
         <v>3969</v>
-      </c>
-      <c r="B38" t="s">
-        <v>3925</v>
       </c>
       <c r="C38" t="s">
         <v>3897</v>
@@ -40955,7 +41024,7 @@
         <v>3973</v>
       </c>
       <c r="C40" t="s">
-        <v>3897</v>
+        <v>3902</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -40966,7 +41035,7 @@
         <v>3975</v>
       </c>
       <c r="C41" t="s">
-        <v>3897</v>
+        <v>3902</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -41018,7 +41087,7 @@
         <v>3984</v>
       </c>
       <c r="B46" t="s">
-        <v>3985</v>
+        <v>3936</v>
       </c>
       <c r="C46" t="s">
         <v>3897</v>
@@ -41026,10 +41095,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
+        <v>3985</v>
+      </c>
+      <c r="B47" t="s">
         <v>3986</v>
-      </c>
-      <c r="B47" t="s">
-        <v>3987</v>
       </c>
       <c r="C47" t="s">
         <v>3897</v>
@@ -41037,10 +41106,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
+        <v>3987</v>
+      </c>
+      <c r="B48" t="s">
         <v>3988</v>
-      </c>
-      <c r="B48" t="s">
-        <v>3989</v>
       </c>
       <c r="C48" t="s">
         <v>3897</v>
@@ -41048,10 +41117,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
+        <v>3989</v>
+      </c>
+      <c r="B49" t="s">
         <v>3990</v>
-      </c>
-      <c r="B49" t="s">
-        <v>3991</v>
       </c>
       <c r="C49" t="s">
         <v>3897</v>
@@ -41059,10 +41128,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
+        <v>3991</v>
+      </c>
+      <c r="B50" t="s">
         <v>3992</v>
-      </c>
-      <c r="B50" t="s">
-        <v>3993</v>
       </c>
       <c r="C50" t="s">
         <v>3897</v>
@@ -41070,21 +41139,21 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
+        <v>3993</v>
+      </c>
+      <c r="B51" t="s">
         <v>3994</v>
       </c>
-      <c r="B51" t="s">
-        <v>3995</v>
-      </c>
       <c r="C51" t="s">
-        <v>3960</v>
+        <v>3897</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
+        <v>3995</v>
+      </c>
+      <c r="B52" t="s">
         <v>3996</v>
-      </c>
-      <c r="B52" t="s">
-        <v>3997</v>
       </c>
       <c r="C52" t="s">
         <v>3897</v>
@@ -41092,10 +41161,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
+        <v>3997</v>
+      </c>
+      <c r="B53" t="s">
         <v>3998</v>
-      </c>
-      <c r="B53" t="s">
-        <v>3999</v>
       </c>
       <c r="C53" t="s">
         <v>3897</v>
@@ -41103,10 +41172,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
+        <v>3999</v>
+      </c>
+      <c r="B54" t="s">
         <v>4000</v>
-      </c>
-      <c r="B54" t="s">
-        <v>4001</v>
       </c>
       <c r="C54" t="s">
         <v>3897</v>
@@ -41114,10 +41183,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
+        <v>4001</v>
+      </c>
+      <c r="B55" t="s">
         <v>4002</v>
-      </c>
-      <c r="B55" t="s">
-        <v>4003</v>
       </c>
       <c r="C55" t="s">
         <v>3897</v>
@@ -41125,10 +41194,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
+        <v>4003</v>
+      </c>
+      <c r="B56" t="s">
         <v>4004</v>
-      </c>
-      <c r="B56" t="s">
-        <v>4005</v>
       </c>
       <c r="C56" t="s">
         <v>3897</v>
@@ -41136,10 +41205,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
+        <v>4005</v>
+      </c>
+      <c r="B57" t="s">
         <v>4006</v>
-      </c>
-      <c r="B57" t="s">
-        <v>4007</v>
       </c>
       <c r="C57" t="s">
         <v>3897</v>
@@ -41147,10 +41216,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
+        <v>4007</v>
+      </c>
+      <c r="B58" t="s">
         <v>4008</v>
-      </c>
-      <c r="B58" t="s">
-        <v>4009</v>
       </c>
       <c r="C58" t="s">
         <v>3897</v>
@@ -41158,10 +41227,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
+        <v>4009</v>
+      </c>
+      <c r="B59" t="s">
         <v>4010</v>
-      </c>
-      <c r="B59" t="s">
-        <v>4011</v>
       </c>
       <c r="C59" t="s">
         <v>3897</v>
@@ -41169,21 +41238,21 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
+        <v>4011</v>
+      </c>
+      <c r="B60" t="s">
         <v>4012</v>
       </c>
-      <c r="B60" t="s">
-        <v>3929</v>
-      </c>
       <c r="C60" t="s">
-        <v>4013</v>
+        <v>3902</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
+        <v>4013</v>
+      </c>
+      <c r="B61" t="s">
         <v>4014</v>
-      </c>
-      <c r="B61" t="s">
-        <v>4015</v>
       </c>
       <c r="C61" t="s">
         <v>3897</v>
@@ -41191,10 +41260,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
+        <v>4015</v>
+      </c>
+      <c r="B62" t="s">
         <v>4016</v>
-      </c>
-      <c r="B62" t="s">
-        <v>4017</v>
       </c>
       <c r="C62" t="s">
         <v>3897</v>
@@ -41202,10 +41271,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
+        <v>4017</v>
+      </c>
+      <c r="B63" t="s">
         <v>4018</v>
-      </c>
-      <c r="B63" t="s">
-        <v>4019</v>
       </c>
       <c r="C63" t="s">
         <v>3897</v>
@@ -41213,10 +41282,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
+        <v>4019</v>
+      </c>
+      <c r="B64" t="s">
         <v>4020</v>
-      </c>
-      <c r="B64" t="s">
-        <v>4021</v>
       </c>
       <c r="C64" t="s">
         <v>3897</v>
@@ -41224,10 +41293,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
+        <v>4021</v>
+      </c>
+      <c r="B65" t="s">
         <v>4022</v>
-      </c>
-      <c r="B65" t="s">
-        <v>4023</v>
       </c>
       <c r="C65" t="s">
         <v>3897</v>
@@ -41235,10 +41304,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
+        <v>4023</v>
+      </c>
+      <c r="B66" t="s">
         <v>4024</v>
-      </c>
-      <c r="B66" t="s">
-        <v>4025</v>
       </c>
       <c r="C66" t="s">
         <v>3897</v>
@@ -41246,10 +41315,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
+        <v>4025</v>
+      </c>
+      <c r="B67" t="s">
         <v>4026</v>
-      </c>
-      <c r="B67" t="s">
-        <v>4027</v>
       </c>
       <c r="C67" t="s">
         <v>3897</v>
@@ -41257,10 +41326,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
+        <v>4027</v>
+      </c>
+      <c r="B68" t="s">
         <v>4028</v>
-      </c>
-      <c r="B68" t="s">
-        <v>4029</v>
       </c>
       <c r="C68" t="s">
         <v>3897</v>
@@ -41268,10 +41337,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
+        <v>4029</v>
+      </c>
+      <c r="B69" t="s">
         <v>4030</v>
-      </c>
-      <c r="B69" t="s">
-        <v>4031</v>
       </c>
       <c r="C69" t="s">
         <v>3897</v>
@@ -41279,21 +41348,21 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
+        <v>4031</v>
+      </c>
+      <c r="B70" t="s">
+        <v>3940</v>
+      </c>
+      <c r="C70" t="s">
         <v>4032</v>
-      </c>
-      <c r="B70" t="s">
-        <v>4033</v>
-      </c>
-      <c r="C70" t="s">
-        <v>3897</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
+        <v>4033</v>
+      </c>
+      <c r="B71" t="s">
         <v>4034</v>
-      </c>
-      <c r="B71" t="s">
-        <v>4035</v>
       </c>
       <c r="C71" t="s">
         <v>3897</v>
@@ -41301,10 +41370,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
+        <v>4035</v>
+      </c>
+      <c r="B72" t="s">
         <v>4036</v>
-      </c>
-      <c r="B72" t="s">
-        <v>4037</v>
       </c>
       <c r="C72" t="s">
         <v>3897</v>
@@ -41312,10 +41381,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
+        <v>4037</v>
+      </c>
+      <c r="B73" t="s">
         <v>4038</v>
-      </c>
-      <c r="B73" t="s">
-        <v>3921</v>
       </c>
       <c r="C73" t="s">
         <v>3897</v>
@@ -41340,7 +41409,7 @@
         <v>4042</v>
       </c>
       <c r="C75" t="s">
-        <v>3897</v>
+        <v>3902</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -41362,6 +41431,138 @@
         <v>4046</v>
       </c>
       <c r="C77" t="s">
+        <v>3897</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" t="s">
+        <v>4047</v>
+      </c>
+      <c r="B78" t="s">
+        <v>4048</v>
+      </c>
+      <c r="C78" t="s">
+        <v>3897</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" t="s">
+        <v>4049</v>
+      </c>
+      <c r="B79" t="s">
+        <v>4050</v>
+      </c>
+      <c r="C79" t="s">
+        <v>3897</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" t="s">
+        <v>4051</v>
+      </c>
+      <c r="B80" t="s">
+        <v>4052</v>
+      </c>
+      <c r="C80" t="s">
+        <v>3897</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" t="s">
+        <v>4053</v>
+      </c>
+      <c r="B81" t="s">
+        <v>4054</v>
+      </c>
+      <c r="C81" t="s">
+        <v>3897</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" t="s">
+        <v>4055</v>
+      </c>
+      <c r="B82" t="s">
+        <v>4056</v>
+      </c>
+      <c r="C82" t="s">
+        <v>3897</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" t="s">
+        <v>4057</v>
+      </c>
+      <c r="B83" t="s">
+        <v>4058</v>
+      </c>
+      <c r="C83" t="s">
+        <v>3897</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" t="s">
+        <v>4059</v>
+      </c>
+      <c r="B84" t="s">
+        <v>4060</v>
+      </c>
+      <c r="C84" t="s">
+        <v>3897</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" t="s">
+        <v>4061</v>
+      </c>
+      <c r="B85" t="s">
+        <v>3932</v>
+      </c>
+      <c r="C85" t="s">
+        <v>3897</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" t="s">
+        <v>4062</v>
+      </c>
+      <c r="B86" t="s">
+        <v>4063</v>
+      </c>
+      <c r="C86" t="s">
+        <v>3897</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" t="s">
+        <v>4064</v>
+      </c>
+      <c r="B87" t="s">
+        <v>4065</v>
+      </c>
+      <c r="C87" t="s">
+        <v>3897</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" t="s">
+        <v>4066</v>
+      </c>
+      <c r="B88" t="s">
+        <v>4067</v>
+      </c>
+      <c r="C88" t="s">
+        <v>3897</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" t="s">
+        <v>4068</v>
+      </c>
+      <c r="B89" t="s">
+        <v>4069</v>
+      </c>
+      <c r="C89" t="s">
         <v>3897</v>
       </c>
     </row>
